--- a/data/raw/김포 25년/항공통계상세조회(노선) (10).xlsx
+++ b/data/raw/김포 25년/항공통계상세조회(노선) (10).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="67">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>11544</t>
-  </si>
-  <si>
-    <t>2090436</t>
-  </si>
-  <si>
-    <t>16731</t>
+    <t>5788</t>
+  </si>
+  <si>
+    <t>1053150</t>
+  </si>
+  <si>
+    <t>8439</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,172 +53,166 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>495</t>
-  </si>
-  <si>
-    <t>84840</t>
-  </si>
-  <si>
-    <t>872</t>
+    <t>248</t>
+  </si>
+  <si>
+    <t>42108</t>
+  </si>
+  <si>
+    <t>419</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>7562</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>749</t>
+  </si>
+  <si>
+    <t>117343</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>나고야(NGO)</t>
+  </si>
+  <si>
+    <t>9371</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>5751</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>78025</t>
+  </si>
+  <si>
+    <t>1564</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>10548</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>7995</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>10015</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>11265</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>11620</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3679</t>
+  </si>
+  <si>
+    <t>705630</t>
+  </si>
+  <si>
+    <t>4972</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>7901</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>2615</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
+  </si>
+  <si>
     <t>124</t>
   </si>
   <si>
-    <t>15611</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1521</t>
-  </si>
-  <si>
-    <t>236068</t>
-  </si>
-  <si>
-    <t>985</t>
-  </si>
-  <si>
-    <t>나고야(NGO)</t>
-  </si>
-  <si>
-    <t>19109</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>11415</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>744</t>
-  </si>
-  <si>
-    <t>156749</t>
-  </si>
-  <si>
-    <t>2532</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>21096</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>16366</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>20170</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>23055</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>23803</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>7307</t>
-  </si>
-  <si>
-    <t>1390797</t>
-  </si>
-  <si>
-    <t>10237</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>16379</t>
-  </si>
-  <si>
-    <t>177</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>4862</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>50116</t>
-  </si>
-  <si>
-    <t>786</t>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>316</t>
   </si>
 </sst>
 </file>
@@ -503,13 +497,13 @@
         <v>45</v>
       </c>
       <c r="D12" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="E12" t="s" s="0">
+      <c r="F12" t="s" s="0">
         <v>47</v>
-      </c>
-      <c r="F12" t="s" s="0">
-        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -520,16 +514,16 @@
         <v>11</v>
       </c>
       <c r="C13" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="D13" t="s" s="0">
+      <c r="E13" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="E13" t="s" s="0">
+      <c r="F13" t="s" s="0">
         <v>51</v>
-      </c>
-      <c r="F13" t="s" s="0">
-        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -540,16 +534,16 @@
         <v>11</v>
       </c>
       <c r="C14" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="D14" t="s" s="0">
+      <c r="E14" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="E14" t="s" s="0">
+      <c r="F14" t="s" s="0">
         <v>55</v>
-      </c>
-      <c r="F14" t="s" s="0">
-        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -560,16 +554,16 @@
         <v>11</v>
       </c>
       <c r="C15" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="D15" t="s" s="0">
+      <c r="E15" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="E15" t="s" s="0">
+      <c r="F15" t="s" s="0">
         <v>59</v>
-      </c>
-      <c r="F15" t="s" s="0">
-        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -580,16 +574,16 @@
         <v>11</v>
       </c>
       <c r="C16" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="D16" t="s" s="0">
+      <c r="F16" t="s" s="0">
         <v>62</v>
-      </c>
-      <c r="E16" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="F16" t="s" s="0">
-        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -600,16 +594,16 @@
         <v>11</v>
       </c>
       <c r="C17" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="E17" t="s" s="0">
         <v>65</v>
       </c>
-      <c r="D17" t="s" s="0">
+      <c r="F17" t="s" s="0">
         <v>66</v>
-      </c>
-      <c r="E17" t="s" s="0">
-        <v>67</v>
-      </c>
-      <c r="F17" t="s" s="0">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
